--- a/asignaturas/BI/EXCEL/Evaluacion2/noviembre/Martes 26 noviembre/ejercicios.xlsx
+++ b/asignaturas/BI/EXCEL/Evaluacion2/noviembre/Martes 26 noviembre/ejercicios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DAW\asignaturas\BI\EXCEL\Evaluacion2\noviembre\Martes 26 noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7FC3D57-0709-4125-AD6B-FF2A7F356ADE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0196CF6B-A015-45D3-847E-144834845F40}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31680" yWindow="2880" windowWidth="21600" windowHeight="11325" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31680" yWindow="2880" windowWidth="21600" windowHeight="11325" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="13" r:id="rId1"/>
@@ -781,7 +781,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1053,43 +1053,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1135,7 +1098,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1223,30 +1186,20 @@
     <xf numFmtId="0" fontId="0" fillId="48" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="43" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="43" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2668,22 +2621,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D67F50D1-3B60-468D-AF79-F1CF6E1C0083}">
-  <dimension ref="D4:I12"/>
+  <dimension ref="D4:H12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="4" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D4" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="G5" s="51" t="s">
+    <row r="5" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="G5" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="52"/>
-      <c r="I5" s="53"/>
-    </row>
-    <row r="6" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="H5" s="46"/>
+    </row>
+    <row r="6" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D6" s="37" t="s">
         <v>19</v>
       </c>
@@ -2693,103 +2645,96 @@
       <c r="G6" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="37"/>
-      <c r="I6" s="37" t="s">
+      <c r="H6" s="37" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D7" s="36">
         <v>1.5</v>
       </c>
-      <c r="E7" s="9">
-        <f>VLOOKUP(D7,G$7:I$12,1,TRUE)</f>
-        <v>0</v>
+      <c r="E7" s="9" t="str">
+        <f>VLOOKUP(D7,G$7:H$12,2,TRUE)</f>
+        <v>SS</v>
       </c>
       <c r="G7" s="36">
         <v>0</v>
       </c>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36" t="s">
+      <c r="H7" s="36" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D8" s="36">
         <v>5.5</v>
       </c>
-      <c r="E8" s="9">
-        <f>VLOOKUP(D8,G$7:I$12,1,TRUE)</f>
-        <v>5</v>
+      <c r="E8" s="9" t="str">
+        <f>VLOOKUP(D8,G$7:H$12,2,TRUE)</f>
+        <v>AP</v>
       </c>
       <c r="G8" s="36">
         <v>5</v>
       </c>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36" t="s">
+      <c r="H8" s="36" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D9" s="36">
         <v>6</v>
       </c>
-      <c r="E9" s="9">
-        <f>VLOOKUP(D9,G$7:I$12,1,TRUE)</f>
-        <v>6</v>
+      <c r="E9" s="9" t="str">
+        <f>VLOOKUP(D9,G$7:H$12,2,TRUE)</f>
+        <v>BIEN</v>
       </c>
       <c r="G9" s="36">
         <v>6</v>
       </c>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36" t="s">
+      <c r="H9" s="36" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D10" s="36">
         <v>8.9</v>
       </c>
-      <c r="E10" s="9">
-        <f>VLOOKUP(D10,G$7:I$12,1,TRUE)</f>
-        <v>7</v>
+      <c r="E10" s="9" t="str">
+        <f>VLOOKUP(D10,G$7:H$12,2,TRUE)</f>
+        <v>NOT</v>
       </c>
       <c r="G10" s="36">
         <v>7</v>
       </c>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36" t="s">
+      <c r="H10" s="36" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D11" s="36">
         <v>10</v>
       </c>
-      <c r="E11" s="9">
-        <f>VLOOKUP(D11,G$7:I$12,1,TRUE)</f>
-        <v>10</v>
+      <c r="E11" s="9" t="str">
+        <f>VLOOKUP(D11,G$7:H$12,2,TRUE)</f>
+        <v>MH</v>
       </c>
       <c r="G11" s="36">
         <v>9</v>
       </c>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36" t="s">
+      <c r="H11" s="36" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="4:8" x14ac:dyDescent="0.3">
       <c r="G12" s="36">
         <v>10</v>
       </c>
-      <c r="H12" s="36"/>
-      <c r="I12" s="36" t="s">
+      <c r="H12" s="36" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="G5:H5"/>
   </mergeCells>
   <conditionalFormatting sqref="D14">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
@@ -2816,11 +2761,11 @@
       <c r="C2" s="6"/>
     </row>
     <row r="4" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="H4" s="45" t="s">
+      <c r="H4" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
     </row>
     <row r="5" spans="3:10" x14ac:dyDescent="0.3">
       <c r="H5" s="7" t="s">
@@ -3054,10 +2999,10 @@
       <c r="M6" s="15"/>
     </row>
     <row r="7" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D7" s="46" t="s">
+      <c r="D7" s="47" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="46"/>
+      <c r="E7" s="47"/>
       <c r="G7" s="16" t="s">
         <v>30</v>
       </c>
@@ -3140,7 +3085,7 @@
         <v>68</v>
       </c>
       <c r="E10" s="30">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G10" s="16" t="s">
         <v>38</v>
@@ -3256,9 +3201,9 @@
       <c r="D14" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="E14" s="50">
-        <f>VLOOKUP(E$9,$G$7:$M$19,_xlfn.IFS(E10=0,4,E10&lt;5,5,E10&lt;10,6,E10&gt;=10,7),TRUE)</f>
-        <v>20</v>
+      <c r="E14" s="45">
+        <f>VLOOKUP(E$9,$G$7:$M$19,_xlfn.IFS(E10=0,4,E10&lt;5,5,E10&lt;10,6,E10&gt;=10,7),FALSE)</f>
+        <v>10</v>
       </c>
       <c r="G14" s="16" t="s">
         <v>49</v>
@@ -3855,26 +3800,26 @@
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="27" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C22" s="27" t="s">
         <v>11</v>
       </c>
       <c r="D22" s="28">
-        <f>VLOOKUP($B$22&amp;$C$22,$B$4:$H$18,4,FALSE)</f>
-        <v>5</v>
+        <f>VLOOKUP($B$22&amp;$C$22,$B$3:$H$18,4,FALSE)</f>
+        <v>8</v>
       </c>
       <c r="E22" s="28">
-        <f>VLOOKUP($B$22&amp;$C$22,$B$4:$H$18,5,FALSE)</f>
-        <v>7</v>
+        <f t="shared" ref="E22:G22" si="2">VLOOKUP($B$22&amp;$C$22,$B$3:$H$18,4,FALSE)</f>
+        <v>8</v>
       </c>
       <c r="F22" s="28">
-        <f>VLOOKUP($B$22&amp;$C$22,$B$4:$H$18,6,FALSE)</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="G22" s="49">
-        <f>VLOOKUP($B$22&amp;$C$22,$B$4:$H$18,7,FALSE)</f>
-        <v>6.666666666666667</v>
+      <c r="G22" s="28">
+        <f t="shared" si="2"/>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3979,14 +3924,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
     </row>
     <row r="2" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
